--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -2510,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846352</v>
+        <v>119846699</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474926</v>
+        <v>474963</v>
       </c>
       <c r="R19" t="n">
-        <v>6825118</v>
+        <v>6825234</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846448</v>
+        <v>119846352</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474930</v>
+        <v>474926</v>
       </c>
       <c r="R20" t="n">
-        <v>6825170</v>
+        <v>6825118</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846699</v>
+        <v>119846448</v>
       </c>
       <c r="B21" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474963</v>
+        <v>474930</v>
       </c>
       <c r="R21" t="n">
-        <v>6825234</v>
+        <v>6825170</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846339</v>
+        <v>119846688</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474938</v>
+        <v>474965</v>
       </c>
       <c r="R2" t="n">
-        <v>6825033</v>
+        <v>6825241</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846320</v>
+        <v>119846457</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474941</v>
+        <v>474924</v>
       </c>
       <c r="R3" t="n">
-        <v>6825028</v>
+        <v>6825196</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846468</v>
+        <v>119846443</v>
       </c>
       <c r="B4" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +909,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474930</v>
+        <v>474931</v>
       </c>
       <c r="R4" t="n">
-        <v>6825208</v>
+        <v>6825157</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846436</v>
+        <v>119846465</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474929</v>
+        <v>474936</v>
       </c>
       <c r="R5" t="n">
-        <v>6825154</v>
+        <v>6825217</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846763</v>
+        <v>119846805</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1151,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474968</v>
+        <v>474958</v>
       </c>
       <c r="R6" t="n">
-        <v>6825269</v>
+        <v>6825288</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1187,11 +1197,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846465</v>
+        <v>119846725</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1266,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474936</v>
+        <v>474946</v>
       </c>
       <c r="R7" t="n">
-        <v>6825217</v>
+        <v>6825245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846343</v>
+        <v>119846468</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474926</v>
+        <v>474930</v>
       </c>
       <c r="R8" t="n">
-        <v>6825058</v>
+        <v>6825208</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846787</v>
+        <v>119846719</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,26 +1455,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474958</v>
+        <v>474951</v>
       </c>
       <c r="R9" t="n">
-        <v>6825278</v>
+        <v>6825242</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1521,7 +1531,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846725</v>
+        <v>119846346</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,31 +1565,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474946</v>
+        <v>474908</v>
       </c>
       <c r="R10" t="n">
-        <v>6825245</v>
+        <v>6825075</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,6 +1636,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1655,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846719</v>
+        <v>119846436</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474951</v>
+        <v>474929</v>
       </c>
       <c r="R11" t="n">
-        <v>6825242</v>
+        <v>6825154</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846473</v>
+        <v>119846790</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1808,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474950</v>
+        <v>474959</v>
       </c>
       <c r="R12" t="n">
-        <v>6825226</v>
+        <v>6825285</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1870,7 +1875,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846349</v>
+        <v>119846452</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474914</v>
+        <v>474929</v>
       </c>
       <c r="R13" t="n">
-        <v>6825101</v>
+        <v>6825179</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846346</v>
+        <v>119846352</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474908</v>
+        <v>474926</v>
       </c>
       <c r="R14" t="n">
-        <v>6825075</v>
+        <v>6825118</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2082,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846452</v>
+        <v>119846763</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,26 +2103,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2125,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474929</v>
+        <v>474968</v>
       </c>
       <c r="R15" t="n">
-        <v>6825179</v>
+        <v>6825269</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,13 +2173,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringar</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2202,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846476</v>
+        <v>119846787</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2231,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474951</v>
+        <v>474958</v>
       </c>
       <c r="R16" t="n">
-        <v>6825228</v>
+        <v>6825278</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2294,7 +2308,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846785</v>
+        <v>119846320</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2337,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474961</v>
+        <v>474941</v>
       </c>
       <c r="R17" t="n">
-        <v>6825278</v>
+        <v>6825028</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2400,7 +2414,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846805</v>
+        <v>119846316</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2448,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474958</v>
+        <v>474928</v>
       </c>
       <c r="R18" t="n">
-        <v>6825288</v>
+        <v>6825005</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2484,6 +2498,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846699</v>
+        <v>119846476</v>
       </c>
       <c r="B19" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,21 +2545,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474963</v>
+        <v>474951</v>
       </c>
       <c r="R19" t="n">
-        <v>6825234</v>
+        <v>6825228</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2616,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846352</v>
+        <v>119846349</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2659,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474926</v>
+        <v>474914</v>
       </c>
       <c r="R20" t="n">
-        <v>6825118</v>
+        <v>6825101</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2722,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846448</v>
+        <v>119846473</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,26 +2757,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474930</v>
+        <v>474950</v>
       </c>
       <c r="R21" t="n">
-        <v>6825170</v>
+        <v>6825226</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2809,7 +2833,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2828,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846306</v>
+        <v>119846699</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2844,31 +2867,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2876,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474922</v>
+        <v>474963</v>
       </c>
       <c r="R22" t="n">
-        <v>6825012</v>
+        <v>6825234</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2920,6 +2938,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2938,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846443</v>
+        <v>119846448</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,31 +2973,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2986,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474931</v>
+        <v>474930</v>
       </c>
       <c r="R23" t="n">
-        <v>6825157</v>
+        <v>6825170</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3030,6 +3044,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3048,7 +3063,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846790</v>
+        <v>119846306</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3096,10 +3111,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474959</v>
+        <v>474922</v>
       </c>
       <c r="R24" t="n">
-        <v>6825285</v>
+        <v>6825012</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3158,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119846457</v>
+        <v>119846339</v>
       </c>
       <c r="B25" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3170,36 +3185,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3207,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474924</v>
+        <v>474938</v>
       </c>
       <c r="R25" t="n">
-        <v>6825196</v>
+        <v>6825033</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3270,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846316</v>
+        <v>119846343</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,31 +3295,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3318,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474928</v>
+        <v>474926</v>
       </c>
       <c r="R26" t="n">
-        <v>6825005</v>
+        <v>6825058</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3356,17 +3360,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846688</v>
+        <v>119846785</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474965</v>
+        <v>474961</v>
       </c>
       <c r="R27" t="n">
-        <v>6825241</v>
+        <v>6825278</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846699</v>
+        <v>119846448</v>
       </c>
       <c r="B22" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,21 +2867,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474963</v>
+        <v>474930</v>
       </c>
       <c r="R22" t="n">
-        <v>6825234</v>
+        <v>6825170</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846448</v>
+        <v>119846699</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474930</v>
+        <v>474963</v>
       </c>
       <c r="R23" t="n">
-        <v>6825170</v>
+        <v>6825234</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846688</v>
+        <v>119846790</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474965</v>
+        <v>474959</v>
       </c>
       <c r="R2" t="n">
-        <v>6825241</v>
+        <v>6825285</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846457</v>
+        <v>119846452</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,36 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474924</v>
+        <v>474929</v>
       </c>
       <c r="R3" t="n">
-        <v>6825196</v>
+        <v>6825179</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846443</v>
+        <v>119846457</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,33 +903,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474931</v>
+        <v>474924</v>
       </c>
       <c r="R4" t="n">
-        <v>6825157</v>
+        <v>6825196</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846465</v>
+        <v>119846320</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,31 +1019,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474936</v>
+        <v>474941</v>
       </c>
       <c r="R5" t="n">
-        <v>6825217</v>
+        <v>6825028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,6 +1090,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846805</v>
+        <v>119846349</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,31 +1125,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474958</v>
+        <v>474914</v>
       </c>
       <c r="R6" t="n">
-        <v>6825288</v>
+        <v>6825101</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,6 +1196,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846725</v>
+        <v>119846306</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1271,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474946</v>
+        <v>474922</v>
       </c>
       <c r="R7" t="n">
-        <v>6825245</v>
+        <v>6825012</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846468</v>
+        <v>119846465</v>
       </c>
       <c r="B8" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,26 +1341,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474930</v>
+        <v>474936</v>
       </c>
       <c r="R8" t="n">
-        <v>6825208</v>
+        <v>6825217</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,7 +1417,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1439,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846719</v>
+        <v>119846787</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,31 +1451,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1487,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474951</v>
+        <v>474958</v>
       </c>
       <c r="R9" t="n">
-        <v>6825242</v>
+        <v>6825278</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1531,6 +1522,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1655,7 +1647,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846436</v>
+        <v>119846719</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1703,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474929</v>
+        <v>474951</v>
       </c>
       <c r="R11" t="n">
-        <v>6825154</v>
+        <v>6825242</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846790</v>
+        <v>119846352</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,31 +1773,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1813,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474959</v>
+        <v>474926</v>
       </c>
       <c r="R12" t="n">
-        <v>6825285</v>
+        <v>6825118</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,6 +1844,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1875,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846452</v>
+        <v>119846688</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1918,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474929</v>
+        <v>474965</v>
       </c>
       <c r="R13" t="n">
-        <v>6825179</v>
+        <v>6825241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846352</v>
+        <v>119846468</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474926</v>
+        <v>474930</v>
       </c>
       <c r="R14" t="n">
-        <v>6825118</v>
+        <v>6825208</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846763</v>
+        <v>119846436</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2135,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474968</v>
+        <v>474929</v>
       </c>
       <c r="R15" t="n">
-        <v>6825269</v>
+        <v>6825154</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,11 +2159,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,7 +2185,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846787</v>
+        <v>119846448</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2245,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474958</v>
+        <v>474930</v>
       </c>
       <c r="R16" t="n">
-        <v>6825278</v>
+        <v>6825170</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2308,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846320</v>
+        <v>119846343</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2351,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474941</v>
+        <v>474926</v>
       </c>
       <c r="R17" t="n">
-        <v>6825028</v>
+        <v>6825058</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2414,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846316</v>
+        <v>119846443</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2462,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474928</v>
+        <v>474931</v>
       </c>
       <c r="R18" t="n">
-        <v>6825005</v>
+        <v>6825157</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2498,11 +2481,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846476</v>
+        <v>119846763</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2545,26 +2523,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2572,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474951</v>
+        <v>474968</v>
       </c>
       <c r="R19" t="n">
-        <v>6825228</v>
+        <v>6825269</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2610,13 +2593,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringar</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2635,10 +2622,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846349</v>
+        <v>119846805</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,26 +2638,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2678,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474914</v>
+        <v>474958</v>
       </c>
       <c r="R20" t="n">
-        <v>6825101</v>
+        <v>6825288</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2722,7 +2714,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2741,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846473</v>
+        <v>119846699</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,31 +2748,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2789,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474950</v>
+        <v>474963</v>
       </c>
       <c r="R21" t="n">
-        <v>6825226</v>
+        <v>6825234</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2833,6 +2819,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2851,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846448</v>
+        <v>119846725</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,26 +2854,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2894,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474930</v>
+        <v>474946</v>
       </c>
       <c r="R22" t="n">
-        <v>6825170</v>
+        <v>6825245</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2938,7 +2930,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2957,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846699</v>
+        <v>119846473</v>
       </c>
       <c r="B23" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,26 +2964,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474963</v>
+        <v>474950</v>
       </c>
       <c r="R23" t="n">
-        <v>6825234</v>
+        <v>6825226</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3044,7 +3040,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3063,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846306</v>
+        <v>119846785</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,31 +3074,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3111,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474922</v>
+        <v>474961</v>
       </c>
       <c r="R24" t="n">
-        <v>6825012</v>
+        <v>6825278</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3155,6 +3145,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3270,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846343</v>
+        <v>119846316</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,26 +3286,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3322,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474926</v>
+        <v>474928</v>
       </c>
       <c r="R26" t="n">
-        <v>6825058</v>
+        <v>6825005</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3360,13 +3356,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846785</v>
+        <v>119846476</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474961</v>
+        <v>474951</v>
       </c>
       <c r="R27" t="n">
-        <v>6825278</v>
+        <v>6825228</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846349</v>
+        <v>119846306</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,26 +1125,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474914</v>
+        <v>474922</v>
       </c>
       <c r="R6" t="n">
-        <v>6825101</v>
+        <v>6825012</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,7 +1201,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846306</v>
+        <v>119846465</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1263,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474922</v>
+        <v>474936</v>
       </c>
       <c r="R7" t="n">
-        <v>6825012</v>
+        <v>6825217</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846465</v>
+        <v>119846349</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,31 +1345,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474936</v>
+        <v>474914</v>
       </c>
       <c r="R8" t="n">
-        <v>6825217</v>
+        <v>6825101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,6 +1416,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846719</v>
+        <v>119846352</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,31 +1663,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474951</v>
+        <v>474926</v>
       </c>
       <c r="R11" t="n">
-        <v>6825242</v>
+        <v>6825118</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1757,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846352</v>
+        <v>119846719</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,26 +1769,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1800,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474926</v>
+        <v>474951</v>
       </c>
       <c r="R12" t="n">
-        <v>6825118</v>
+        <v>6825242</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,7 +1845,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846790</v>
+        <v>119846699</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474959</v>
+        <v>474963</v>
       </c>
       <c r="R2" t="n">
-        <v>6825285</v>
+        <v>6825234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846452</v>
+        <v>119846473</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474929</v>
+        <v>474950</v>
       </c>
       <c r="R3" t="n">
-        <v>6825179</v>
+        <v>6825226</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846457</v>
+        <v>119846352</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,36 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474924</v>
+        <v>474926</v>
       </c>
       <c r="R4" t="n">
-        <v>6825196</v>
+        <v>6825118</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846320</v>
+        <v>119846805</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,26 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474941</v>
+        <v>474958</v>
       </c>
       <c r="R5" t="n">
-        <v>6825028</v>
+        <v>6825288</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846306</v>
+        <v>119846790</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1157,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474922</v>
+        <v>474959</v>
       </c>
       <c r="R6" t="n">
-        <v>6825012</v>
+        <v>6825285</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846465</v>
+        <v>119846316</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1267,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474936</v>
+        <v>474928</v>
       </c>
       <c r="R7" t="n">
-        <v>6825217</v>
+        <v>6825005</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,6 +1301,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846349</v>
+        <v>119846343</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1372,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474914</v>
+        <v>474926</v>
       </c>
       <c r="R8" t="n">
-        <v>6825101</v>
+        <v>6825058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1541,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846346</v>
+        <v>119846436</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,26 +1560,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1584,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474908</v>
+        <v>474929</v>
       </c>
       <c r="R10" t="n">
-        <v>6825075</v>
+        <v>6825154</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,7 +1636,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1647,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846352</v>
+        <v>119846443</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,26 +1670,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1690,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474926</v>
+        <v>474931</v>
       </c>
       <c r="R11" t="n">
-        <v>6825118</v>
+        <v>6825157</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,7 +1746,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846719</v>
+        <v>119846339</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,31 +1780,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1801,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474951</v>
+        <v>474938</v>
       </c>
       <c r="R12" t="n">
-        <v>6825242</v>
+        <v>6825033</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,6 +1851,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846688</v>
+        <v>119846306</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,26 +1886,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1906,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474965</v>
+        <v>474922</v>
       </c>
       <c r="R13" t="n">
-        <v>6825241</v>
+        <v>6825012</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1950,7 +1962,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846468</v>
+        <v>119846785</v>
       </c>
       <c r="B14" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,21 +1996,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474930</v>
+        <v>474961</v>
       </c>
       <c r="R14" t="n">
-        <v>6825208</v>
+        <v>6825278</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2075,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846436</v>
+        <v>119846349</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,31 +2102,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474929</v>
+        <v>474914</v>
       </c>
       <c r="R15" t="n">
-        <v>6825154</v>
+        <v>6825101</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2167,6 +2173,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2185,7 +2192,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846448</v>
+        <v>119846346</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2228,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474930</v>
+        <v>474908</v>
       </c>
       <c r="R16" t="n">
-        <v>6825170</v>
+        <v>6825075</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2291,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846343</v>
+        <v>119846452</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2334,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474926</v>
+        <v>474929</v>
       </c>
       <c r="R17" t="n">
-        <v>6825058</v>
+        <v>6825179</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2397,7 +2404,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846443</v>
+        <v>119846465</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2445,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474931</v>
+        <v>474936</v>
       </c>
       <c r="R18" t="n">
-        <v>6825157</v>
+        <v>6825217</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2507,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846763</v>
+        <v>119846448</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,31 +2530,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2555,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474968</v>
+        <v>474930</v>
       </c>
       <c r="R19" t="n">
-        <v>6825269</v>
+        <v>6825170</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2593,17 +2595,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringar</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2622,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846805</v>
+        <v>119846476</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,31 +2636,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2670,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474958</v>
+        <v>474951</v>
       </c>
       <c r="R20" t="n">
-        <v>6825288</v>
+        <v>6825228</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,6 +2707,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2732,10 +2726,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846699</v>
+        <v>119846719</v>
       </c>
       <c r="B21" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,26 +2742,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2775,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474963</v>
+        <v>474951</v>
       </c>
       <c r="R21" t="n">
-        <v>6825234</v>
+        <v>6825242</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2819,7 +2818,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2948,7 +2946,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846473</v>
+        <v>119846763</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2996,10 +2994,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474950</v>
+        <v>474968</v>
       </c>
       <c r="R23" t="n">
-        <v>6825226</v>
+        <v>6825269</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3032,6 +3030,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,7 +3061,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846785</v>
+        <v>119846688</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3101,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474961</v>
+        <v>474965</v>
       </c>
       <c r="R24" t="n">
-        <v>6825278</v>
+        <v>6825241</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3164,7 +3167,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119846339</v>
+        <v>119846320</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3207,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474938</v>
+        <v>474941</v>
       </c>
       <c r="R25" t="n">
-        <v>6825033</v>
+        <v>6825028</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3270,10 +3273,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846316</v>
+        <v>119846468</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,31 +3289,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3318,10 +3316,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474928</v>
+        <v>474930</v>
       </c>
       <c r="R26" t="n">
-        <v>6825005</v>
+        <v>6825208</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3356,17 +3354,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,10 +3379,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846476</v>
+        <v>119846457</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>5169</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,30 +3391,36 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474951</v>
+        <v>474924</v>
       </c>
       <c r="R27" t="n">
-        <v>6825228</v>
+        <v>6825196</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846352</v>
+        <v>119846805</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +907,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474926</v>
+        <v>474958</v>
       </c>
       <c r="R4" t="n">
-        <v>6825118</v>
+        <v>6825288</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846805</v>
+        <v>119846352</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R5" t="n">
-        <v>6825288</v>
+        <v>6825118</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846805</v>
+        <v>119846352</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R4" t="n">
-        <v>6825288</v>
+        <v>6825118</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846352</v>
+        <v>119846805</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,26 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474926</v>
+        <v>474958</v>
       </c>
       <c r="R5" t="n">
-        <v>6825118</v>
+        <v>6825288</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846465</v>
+        <v>119846448</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,31 +2420,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474936</v>
+        <v>474930</v>
       </c>
       <c r="R18" t="n">
-        <v>6825217</v>
+        <v>6825170</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2496,6 +2491,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2514,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846448</v>
+        <v>119846465</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2530,26 +2526,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474930</v>
+        <v>474936</v>
       </c>
       <c r="R19" t="n">
-        <v>6825170</v>
+        <v>6825217</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2601,7 +2602,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -2404,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846448</v>
+        <v>119846465</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,26 +2420,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474930</v>
+        <v>474936</v>
       </c>
       <c r="R18" t="n">
-        <v>6825170</v>
+        <v>6825217</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2496,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2510,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846465</v>
+        <v>119846448</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,31 +2530,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2558,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474936</v>
+        <v>474930</v>
       </c>
       <c r="R19" t="n">
-        <v>6825217</v>
+        <v>6825170</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2602,6 +2601,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846352</v>
+        <v>119846805</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +907,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474926</v>
+        <v>474958</v>
       </c>
       <c r="R4" t="n">
-        <v>6825118</v>
+        <v>6825288</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846805</v>
+        <v>119846352</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R5" t="n">
-        <v>6825288</v>
+        <v>6825118</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846316</v>
+        <v>119846343</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,31 +1233,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474928</v>
+        <v>474926</v>
       </c>
       <c r="R7" t="n">
-        <v>6825005</v>
+        <v>6825058</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,17 +1298,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846343</v>
+        <v>119846787</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1375,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474926</v>
+        <v>474958</v>
       </c>
       <c r="R8" t="n">
-        <v>6825058</v>
+        <v>6825278</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846787</v>
+        <v>119846316</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,26 +1445,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474958</v>
+        <v>474928</v>
       </c>
       <c r="R9" t="n">
-        <v>6825278</v>
+        <v>6825005</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,13 +1515,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846805</v>
+        <v>119846352</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R4" t="n">
-        <v>6825288</v>
+        <v>6825118</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846352</v>
+        <v>119846805</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,26 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474926</v>
+        <v>474958</v>
       </c>
       <c r="R5" t="n">
-        <v>6825118</v>
+        <v>6825288</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846343</v>
+        <v>119846316</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,26 +1233,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474926</v>
+        <v>474928</v>
       </c>
       <c r="R7" t="n">
-        <v>6825058</v>
+        <v>6825005</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,13 +1303,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1323,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846787</v>
+        <v>119846343</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1366,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R8" t="n">
-        <v>6825278</v>
+        <v>6825058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846316</v>
+        <v>119846787</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,31 +1454,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474928</v>
+        <v>474958</v>
       </c>
       <c r="R9" t="n">
-        <v>6825005</v>
+        <v>6825278</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1515,17 +1519,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846465</v>
+        <v>119846448</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,31 +2420,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474936</v>
+        <v>474930</v>
       </c>
       <c r="R18" t="n">
-        <v>6825217</v>
+        <v>6825170</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2496,6 +2491,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2514,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846448</v>
+        <v>119846465</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2530,26 +2526,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474930</v>
+        <v>474936</v>
       </c>
       <c r="R19" t="n">
-        <v>6825170</v>
+        <v>6825217</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2601,7 +2602,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846699</v>
+        <v>119846320</v>
       </c>
       <c r="B2" t="n">
-        <v>78560</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474963</v>
+        <v>474941</v>
       </c>
       <c r="R2" t="n">
-        <v>6825234</v>
+        <v>6825028</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846473</v>
+        <v>119846805</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474950</v>
+        <v>474958</v>
       </c>
       <c r="R3" t="n">
-        <v>6825226</v>
+        <v>6825288</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846352</v>
+        <v>119846790</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +907,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474926</v>
+        <v>474959</v>
       </c>
       <c r="R4" t="n">
-        <v>6825118</v>
+        <v>6825285</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846805</v>
+        <v>119846343</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R5" t="n">
-        <v>6825288</v>
+        <v>6825058</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846790</v>
+        <v>119846452</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,31 +1123,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474959</v>
+        <v>474929</v>
       </c>
       <c r="R6" t="n">
-        <v>6825285</v>
+        <v>6825179</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846316</v>
+        <v>119846352</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,31 +1229,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474928</v>
+        <v>474926</v>
       </c>
       <c r="R7" t="n">
-        <v>6825005</v>
+        <v>6825118</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,17 +1294,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846343</v>
+        <v>119846436</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,26 +1335,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474926</v>
+        <v>474929</v>
       </c>
       <c r="R8" t="n">
-        <v>6825058</v>
+        <v>6825154</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846787</v>
+        <v>119846306</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,26 +1445,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474958</v>
+        <v>474922</v>
       </c>
       <c r="R9" t="n">
-        <v>6825278</v>
+        <v>6825012</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846436</v>
+        <v>119846346</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,31 +1555,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1592,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474929</v>
+        <v>474908</v>
       </c>
       <c r="R10" t="n">
-        <v>6825154</v>
+        <v>6825075</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1636,6 +1626,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1654,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846443</v>
+        <v>119846719</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474931</v>
+        <v>474951</v>
       </c>
       <c r="R11" t="n">
-        <v>6825157</v>
+        <v>6825242</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846339</v>
+        <v>119846785</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474938</v>
+        <v>474961</v>
       </c>
       <c r="R12" t="n">
-        <v>6825033</v>
+        <v>6825278</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1870,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846306</v>
+        <v>119846468</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,31 +1877,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1918,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474922</v>
+        <v>474930</v>
       </c>
       <c r="R13" t="n">
-        <v>6825012</v>
+        <v>6825208</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1962,6 +1948,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1980,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846785</v>
+        <v>119846349</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474961</v>
+        <v>474914</v>
       </c>
       <c r="R14" t="n">
-        <v>6825278</v>
+        <v>6825101</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2086,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846349</v>
+        <v>119846339</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474914</v>
+        <v>474938</v>
       </c>
       <c r="R15" t="n">
-        <v>6825101</v>
+        <v>6825033</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846346</v>
+        <v>119846688</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474908</v>
+        <v>474965</v>
       </c>
       <c r="R16" t="n">
-        <v>6825075</v>
+        <v>6825241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846452</v>
+        <v>119846476</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474929</v>
+        <v>474951</v>
       </c>
       <c r="R17" t="n">
-        <v>6825179</v>
+        <v>6825228</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2404,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846448</v>
+        <v>119846725</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,26 +2407,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474930</v>
+        <v>474946</v>
       </c>
       <c r="R18" t="n">
-        <v>6825170</v>
+        <v>6825245</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2491,7 +2483,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2513,7 +2504,7 @@
         <v>119846465</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846476</v>
+        <v>119846787</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2663,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474951</v>
+        <v>474958</v>
       </c>
       <c r="R20" t="n">
-        <v>6825228</v>
+        <v>6825278</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2726,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846719</v>
+        <v>119846443</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474951</v>
+        <v>474931</v>
       </c>
       <c r="R21" t="n">
-        <v>6825242</v>
+        <v>6825157</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846725</v>
+        <v>119846763</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2884,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474946</v>
+        <v>474968</v>
       </c>
       <c r="R22" t="n">
-        <v>6825245</v>
+        <v>6825269</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2920,6 +2911,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846763</v>
+        <v>119846457</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>5169</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2958,33 +2954,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2994,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474968</v>
+        <v>474924</v>
       </c>
       <c r="R23" t="n">
-        <v>6825269</v>
+        <v>6825196</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3032,17 +3029,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringar</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3061,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846688</v>
+        <v>119846699</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3077,21 +3070,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3104,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474965</v>
+        <v>474963</v>
       </c>
       <c r="R24" t="n">
-        <v>6825241</v>
+        <v>6825234</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3167,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119846320</v>
+        <v>119846448</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3210,10 +3203,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474941</v>
+        <v>474930</v>
       </c>
       <c r="R25" t="n">
-        <v>6825028</v>
+        <v>6825170</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3273,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846468</v>
+        <v>119846316</v>
       </c>
       <c r="B26" t="n">
-        <v>78560</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,26 +3282,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3316,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474930</v>
+        <v>474928</v>
       </c>
       <c r="R26" t="n">
-        <v>6825208</v>
+        <v>6825005</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3354,13 +3352,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3379,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846457</v>
+        <v>119846473</v>
       </c>
       <c r="B27" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,34 +3393,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3428,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474924</v>
+        <v>474950</v>
       </c>
       <c r="R27" t="n">
-        <v>6825196</v>
+        <v>6825226</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3472,7 +3473,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846805</v>
+        <v>119846343</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R3" t="n">
-        <v>6825288</v>
+        <v>6825058</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846790</v>
+        <v>119846452</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474959</v>
+        <v>474929</v>
       </c>
       <c r="R4" t="n">
-        <v>6825285</v>
+        <v>6825179</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846343</v>
+        <v>119846352</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1047,7 +1039,7 @@
         <v>474926</v>
       </c>
       <c r="R5" t="n">
-        <v>6825058</v>
+        <v>6825118</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846452</v>
+        <v>119846790</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,26 +1115,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474929</v>
+        <v>474959</v>
       </c>
       <c r="R6" t="n">
-        <v>6825179</v>
+        <v>6825285</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1191,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846352</v>
+        <v>119846805</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,26 +1225,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474926</v>
+        <v>474958</v>
       </c>
       <c r="R7" t="n">
-        <v>6825118</v>
+        <v>6825288</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846343</v>
+        <v>119846725</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474926</v>
+        <v>474946</v>
       </c>
       <c r="R3" t="n">
-        <v>6825058</v>
+        <v>6825245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846452</v>
+        <v>119846805</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +907,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474929</v>
+        <v>474958</v>
       </c>
       <c r="R4" t="n">
-        <v>6825179</v>
+        <v>6825288</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846352</v>
+        <v>119846443</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1017,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474926</v>
+        <v>474931</v>
       </c>
       <c r="R5" t="n">
-        <v>6825118</v>
+        <v>6825157</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846790</v>
+        <v>119846436</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1147,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474959</v>
+        <v>474929</v>
       </c>
       <c r="R6" t="n">
-        <v>6825285</v>
+        <v>6825154</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846805</v>
+        <v>119846343</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,31 +1237,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R7" t="n">
-        <v>6825288</v>
+        <v>6825058</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1301,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846436</v>
+        <v>119846316</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1367,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474929</v>
+        <v>474928</v>
       </c>
       <c r="R8" t="n">
-        <v>6825154</v>
+        <v>6825005</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1403,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846306</v>
+        <v>119846473</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1477,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474922</v>
+        <v>474950</v>
       </c>
       <c r="R9" t="n">
-        <v>6825012</v>
+        <v>6825226</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1539,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846346</v>
+        <v>119846352</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1582,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474908</v>
+        <v>474926</v>
       </c>
       <c r="R10" t="n">
-        <v>6825075</v>
+        <v>6825118</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1645,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846719</v>
+        <v>119846306</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1693,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474951</v>
+        <v>474922</v>
       </c>
       <c r="R11" t="n">
-        <v>6825242</v>
+        <v>6825012</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846785</v>
+        <v>119846790</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,26 +1784,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1798,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474961</v>
+        <v>474959</v>
       </c>
       <c r="R12" t="n">
-        <v>6825278</v>
+        <v>6825285</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1842,7 +1860,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846468</v>
+        <v>119846349</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1894,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1904,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474930</v>
+        <v>474914</v>
       </c>
       <c r="R13" t="n">
-        <v>6825208</v>
+        <v>6825101</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1967,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846349</v>
+        <v>119846787</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2010,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474914</v>
+        <v>474958</v>
       </c>
       <c r="R14" t="n">
-        <v>6825101</v>
+        <v>6825278</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846339</v>
+        <v>119846763</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,26 +2106,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2116,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474938</v>
+        <v>474968</v>
       </c>
       <c r="R15" t="n">
-        <v>6825033</v>
+        <v>6825269</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2154,13 +2176,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringar</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2179,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846688</v>
+        <v>119846465</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,26 +2221,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2222,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474965</v>
+        <v>474936</v>
       </c>
       <c r="R16" t="n">
-        <v>6825241</v>
+        <v>6825217</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2266,7 +2297,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2391,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846725</v>
+        <v>119846785</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,31 +2437,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2439,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474946</v>
+        <v>474961</v>
       </c>
       <c r="R18" t="n">
-        <v>6825245</v>
+        <v>6825278</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2483,6 +2508,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2501,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846465</v>
+        <v>119846457</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,33 +2539,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2549,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474936</v>
+        <v>474924</v>
       </c>
       <c r="R19" t="n">
-        <v>6825217</v>
+        <v>6825196</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2593,6 +2620,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2611,7 +2639,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846787</v>
+        <v>119846346</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2654,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474958</v>
+        <v>474908</v>
       </c>
       <c r="R20" t="n">
-        <v>6825278</v>
+        <v>6825075</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,10 +2745,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846443</v>
+        <v>119846699</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>78576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,31 +2761,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474931</v>
+        <v>474963</v>
       </c>
       <c r="R21" t="n">
-        <v>6825157</v>
+        <v>6825234</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2809,6 +2832,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2827,7 +2851,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846763</v>
+        <v>119846719</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2875,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474968</v>
+        <v>474951</v>
       </c>
       <c r="R22" t="n">
-        <v>6825269</v>
+        <v>6825242</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2911,11 +2935,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846457</v>
+        <v>119846452</v>
       </c>
       <c r="B23" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,36 +2973,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2991,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474924</v>
+        <v>474929</v>
       </c>
       <c r="R23" t="n">
-        <v>6825196</v>
+        <v>6825179</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3054,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846699</v>
+        <v>119846688</v>
       </c>
       <c r="B24" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,21 +3083,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3097,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474963</v>
+        <v>474965</v>
       </c>
       <c r="R24" t="n">
-        <v>6825234</v>
+        <v>6825241</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3160,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119846448</v>
+        <v>119846468</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3176,21 +3189,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,7 +3219,7 @@
         <v>474930</v>
       </c>
       <c r="R25" t="n">
-        <v>6825170</v>
+        <v>6825208</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3266,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846316</v>
+        <v>119846339</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3282,31 +3295,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3314,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474928</v>
+        <v>474938</v>
       </c>
       <c r="R26" t="n">
-        <v>6825005</v>
+        <v>6825033</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3352,17 +3360,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846473</v>
+        <v>119846448</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,31 +3401,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3429,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474950</v>
+        <v>474930</v>
       </c>
       <c r="R27" t="n">
-        <v>6825226</v>
+        <v>6825170</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3473,6 +3472,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846320</v>
+        <v>119846443</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474941</v>
+        <v>474931</v>
       </c>
       <c r="R2" t="n">
-        <v>6825028</v>
+        <v>6825157</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846725</v>
+        <v>119846473</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -829,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474946</v>
+        <v>474950</v>
       </c>
       <c r="R3" t="n">
-        <v>6825245</v>
+        <v>6825226</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846805</v>
+        <v>119846688</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +911,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474958</v>
+        <v>474965</v>
       </c>
       <c r="R4" t="n">
-        <v>6825288</v>
+        <v>6825241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,6 +982,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846443</v>
+        <v>119846352</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,31 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474931</v>
+        <v>474926</v>
       </c>
       <c r="R5" t="n">
-        <v>6825157</v>
+        <v>6825118</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846436</v>
+        <v>119846316</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1159,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474929</v>
+        <v>474928</v>
       </c>
       <c r="R6" t="n">
-        <v>6825154</v>
+        <v>6825005</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846343</v>
+        <v>119846349</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1264,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474926</v>
+        <v>474914</v>
       </c>
       <c r="R7" t="n">
-        <v>6825058</v>
+        <v>6825101</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1327,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846316</v>
+        <v>119846436</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1375,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474928</v>
+        <v>474929</v>
       </c>
       <c r="R8" t="n">
-        <v>6825005</v>
+        <v>6825154</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846473</v>
+        <v>119846306</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1490,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474950</v>
+        <v>474922</v>
       </c>
       <c r="R9" t="n">
-        <v>6825226</v>
+        <v>6825012</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846352</v>
+        <v>119846725</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,26 +1564,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1595,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474926</v>
+        <v>474946</v>
       </c>
       <c r="R10" t="n">
-        <v>6825118</v>
+        <v>6825245</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,7 +1640,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846306</v>
+        <v>119846805</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474922</v>
+        <v>474958</v>
       </c>
       <c r="R11" t="n">
-        <v>6825012</v>
+        <v>6825288</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846790</v>
+        <v>119846452</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,31 +1784,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1816,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474959</v>
+        <v>474929</v>
       </c>
       <c r="R12" t="n">
-        <v>6825285</v>
+        <v>6825179</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,6 +1855,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1878,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846349</v>
+        <v>119846699</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,21 +1890,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1921,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474914</v>
+        <v>474963</v>
       </c>
       <c r="R13" t="n">
-        <v>6825101</v>
+        <v>6825234</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1984,7 +1980,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846787</v>
+        <v>119846320</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474958</v>
+        <v>474941</v>
       </c>
       <c r="R14" t="n">
-        <v>6825278</v>
+        <v>6825028</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846763</v>
+        <v>119846785</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,31 +2102,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2138,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474968</v>
+        <v>474961</v>
       </c>
       <c r="R15" t="n">
-        <v>6825269</v>
+        <v>6825278</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2176,17 +2167,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringar</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846476</v>
+        <v>119846787</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2358,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474951</v>
+        <v>474958</v>
       </c>
       <c r="R17" t="n">
-        <v>6825228</v>
+        <v>6825278</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2421,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846785</v>
+        <v>119846719</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,26 +2424,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2464,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474961</v>
+        <v>474951</v>
       </c>
       <c r="R18" t="n">
-        <v>6825278</v>
+        <v>6825242</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2508,7 +2500,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846457</v>
+        <v>119846790</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2539,34 +2530,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2576,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474924</v>
+        <v>474959</v>
       </c>
       <c r="R19" t="n">
-        <v>6825196</v>
+        <v>6825285</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2620,7 +2610,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2639,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846346</v>
+        <v>119846763</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,26 +2644,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2682,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474908</v>
+        <v>474968</v>
       </c>
       <c r="R20" t="n">
-        <v>6825075</v>
+        <v>6825269</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2720,13 +2714,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringar</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2745,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846699</v>
+        <v>119846457</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
+        <v>5169</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,30 +2755,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2788,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474963</v>
+        <v>474924</v>
       </c>
       <c r="R21" t="n">
-        <v>6825234</v>
+        <v>6825196</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2851,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846719</v>
+        <v>119846448</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,31 +2871,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2899,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474951</v>
+        <v>474930</v>
       </c>
       <c r="R22" t="n">
-        <v>6825242</v>
+        <v>6825170</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2943,6 +2942,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846452</v>
+        <v>119846476</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474929</v>
+        <v>474951</v>
       </c>
       <c r="R23" t="n">
-        <v>6825179</v>
+        <v>6825228</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846688</v>
+        <v>119846468</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474965</v>
+        <v>474930</v>
       </c>
       <c r="R24" t="n">
-        <v>6825241</v>
+        <v>6825208</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119846468</v>
+        <v>119846339</v>
       </c>
       <c r="B25" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474930</v>
+        <v>474938</v>
       </c>
       <c r="R25" t="n">
-        <v>6825208</v>
+        <v>6825033</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846339</v>
+        <v>119846343</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474938</v>
+        <v>474926</v>
       </c>
       <c r="R26" t="n">
-        <v>6825033</v>
+        <v>6825058</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846448</v>
+        <v>119846346</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474930</v>
+        <v>474908</v>
       </c>
       <c r="R27" t="n">
-        <v>6825170</v>
+        <v>6825075</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -2192,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846465</v>
+        <v>119846787</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,31 +2208,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474936</v>
+        <v>474958</v>
       </c>
       <c r="R16" t="n">
-        <v>6825217</v>
+        <v>6825278</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2284,6 +2279,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2302,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846787</v>
+        <v>119846465</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,26 +2314,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2345,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474958</v>
+        <v>474936</v>
       </c>
       <c r="R17" t="n">
-        <v>6825278</v>
+        <v>6825217</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2389,7 +2390,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846476</v>
+        <v>119846468</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474951</v>
+        <v>474930</v>
       </c>
       <c r="R23" t="n">
-        <v>6825228</v>
+        <v>6825208</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119846468</v>
+        <v>119846476</v>
       </c>
       <c r="B24" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474930</v>
+        <v>474951</v>
       </c>
       <c r="R24" t="n">
-        <v>6825208</v>
+        <v>6825228</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846443</v>
+        <v>119846468</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474931</v>
+        <v>474930</v>
       </c>
       <c r="R2" t="n">
-        <v>6825157</v>
+        <v>6825208</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846473</v>
+        <v>119846725</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -833,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474950</v>
+        <v>474946</v>
       </c>
       <c r="R3" t="n">
-        <v>6825226</v>
+        <v>6825245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846688</v>
+        <v>119846785</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -938,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474965</v>
+        <v>474961</v>
       </c>
       <c r="R4" t="n">
-        <v>6825241</v>
+        <v>6825278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846352</v>
+        <v>119846320</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1044,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474926</v>
+        <v>474941</v>
       </c>
       <c r="R5" t="n">
-        <v>6825118</v>
+        <v>6825028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846316</v>
+        <v>119846452</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,31 +1119,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474928</v>
+        <v>474929</v>
       </c>
       <c r="R6" t="n">
-        <v>6825005</v>
+        <v>6825179</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,17 +1184,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringad tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1222,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846349</v>
+        <v>119846457</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,30 +1221,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474914</v>
+        <v>474924</v>
       </c>
       <c r="R7" t="n">
-        <v>6825101</v>
+        <v>6825196</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846436</v>
+        <v>119846349</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,31 +1337,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474929</v>
+        <v>474914</v>
       </c>
       <c r="R8" t="n">
-        <v>6825154</v>
+        <v>6825101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846306</v>
+        <v>119846352</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,31 +1443,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474922</v>
+        <v>474926</v>
       </c>
       <c r="R9" t="n">
-        <v>6825012</v>
+        <v>6825118</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,6 +1514,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846725</v>
+        <v>119846805</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1596,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474946</v>
+        <v>474958</v>
       </c>
       <c r="R10" t="n">
-        <v>6825245</v>
+        <v>6825288</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846805</v>
+        <v>119846343</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,31 +1659,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474958</v>
+        <v>474926</v>
       </c>
       <c r="R11" t="n">
-        <v>6825288</v>
+        <v>6825058</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1750,6 +1730,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1768,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846452</v>
+        <v>119846787</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1811,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474929</v>
+        <v>474958</v>
       </c>
       <c r="R12" t="n">
-        <v>6825179</v>
+        <v>6825278</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846699</v>
+        <v>119846790</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,26 +1871,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1917,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474963</v>
+        <v>474959</v>
       </c>
       <c r="R13" t="n">
-        <v>6825234</v>
+        <v>6825285</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1961,7 +1947,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1980,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846320</v>
+        <v>119846316</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,26 +1981,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474941</v>
+        <v>474928</v>
       </c>
       <c r="R14" t="n">
-        <v>6825028</v>
+        <v>6825005</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2061,13 +2051,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringad tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846785</v>
+        <v>119846465</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,26 +2096,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474961</v>
+        <v>474936</v>
       </c>
       <c r="R15" t="n">
-        <v>6825278</v>
+        <v>6825217</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,7 +2172,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,7 +2190,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119846787</v>
+        <v>119846346</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2235,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474958</v>
+        <v>474908</v>
       </c>
       <c r="R16" t="n">
-        <v>6825278</v>
+        <v>6825075</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119846465</v>
+        <v>119846699</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>78576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,31 +2312,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2346,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474936</v>
+        <v>474963</v>
       </c>
       <c r="R17" t="n">
-        <v>6825217</v>
+        <v>6825234</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,6 +2383,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119846719</v>
+        <v>119846688</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,31 +2418,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2456,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474951</v>
+        <v>474965</v>
       </c>
       <c r="R18" t="n">
-        <v>6825242</v>
+        <v>6825241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2500,6 +2489,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2518,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119846790</v>
+        <v>119846339</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,31 +2524,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474959</v>
+        <v>474938</v>
       </c>
       <c r="R19" t="n">
-        <v>6825285</v>
+        <v>6825033</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2610,6 +2595,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2628,10 +2614,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119846763</v>
+        <v>119846448</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2644,31 +2630,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2657,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474968</v>
+        <v>474930</v>
       </c>
       <c r="R20" t="n">
-        <v>6825269</v>
+        <v>6825170</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,17 +2695,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringar</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2743,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119846457</v>
+        <v>119846436</v>
       </c>
       <c r="B21" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,34 +2732,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2792,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474924</v>
+        <v>474929</v>
       </c>
       <c r="R21" t="n">
-        <v>6825196</v>
+        <v>6825154</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2836,7 +2812,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2855,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119846448</v>
+        <v>119846306</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,26 +2846,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2898,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474930</v>
+        <v>474922</v>
       </c>
       <c r="R22" t="n">
-        <v>6825170</v>
+        <v>6825012</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2942,7 +2922,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2961,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119846468</v>
+        <v>119846473</v>
       </c>
       <c r="B23" t="n">
-        <v>78576</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,26 +2956,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3004,10 +2988,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474930</v>
+        <v>474950</v>
       </c>
       <c r="R23" t="n">
-        <v>6825208</v>
+        <v>6825226</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3048,7 +3032,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3173,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119846339</v>
+        <v>119846443</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,26 +3172,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3216,10 +3204,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474938</v>
+        <v>474931</v>
       </c>
       <c r="R25" t="n">
-        <v>6825033</v>
+        <v>6825157</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3260,7 +3248,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119846343</v>
+        <v>119846719</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,26 +3282,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474926</v>
+        <v>474951</v>
       </c>
       <c r="R26" t="n">
-        <v>6825058</v>
+        <v>6825242</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3366,7 +3358,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846346</v>
+        <v>119846763</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,26 +3392,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3428,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474908</v>
+        <v>474968</v>
       </c>
       <c r="R27" t="n">
-        <v>6825075</v>
+        <v>6825269</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3466,13 +3462,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringar</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>119846725</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>119846805</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>119846790</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>119846316</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>119846465</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>119846436</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>119846306</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>119846473</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>119846443</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>119846719</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>119846763</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 38458-2023 artfynd.xlsx
+++ b/artfynd/A 38458-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>119846725</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>119846805</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>119846790</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>119846316</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>119846465</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
         <v>119846436</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
         <v>119846306</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>119846473</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
         <v>119846443</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3269,7 +3269,7 @@
         <v>119846719</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>119846763</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
